--- a/docs/testing/generated/A-survivors.xlsx
+++ b/docs/testing/generated/A-survivors.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="StockLOG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full precision" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'StockLOG'!$A$4:$T$14</definedName>
@@ -455,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SYNTHETIC ACCEPTANCE FIXTURE. AUD. Animal selection filters never clip lifetime financials. Unknown purchase cost makes P/L incomplete. Active animals show costs/revenue to date, not final realised sale. Timestamps are Unix seconds; property timezone Australia/Melbourne. Stored allocations retain 12 decimal places.</t>
+          <t>SYNTHETIC ACCEPTANCE FIXTURE. AUD. Date/attribute filters select animals; their finances always cover the full lifetime. Unknown purchase prices make P/L incomplete. Active animals show costs/revenue to date, not a final sale outcome. Export dates use your display timezone. Property timezone Australia/Melbourne. Amounts are displayed to cents with reconciliation rounding; Excel also includes full-precision values.</t>
         </is>
       </c>
     </row>
@@ -467,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"dataset": "animals", "filters": {"mob": "1", "status": "exited"}}</t>
+          <t>Animals; Mob: April; Status: exited; Attributes: current; Filters: all</t>
         </is>
       </c>
     </row>
@@ -581,7 +582,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ee84c0e2-8a4d-41af-a847-6fbcb8ab9775</t>
+          <t>6f1e4aba-15dd-4f6e-9dd2-3fcf3046f1da</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -616,17 +617,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -641,37 +642,37 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1589670000</t>
+          <t>17/05/2020 09:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -683,7 +684,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>d6dc4844-1cc9-4b54-8fa9-c4c278e88d17</t>
+          <t>c1cc6e28-6386-470a-944c-07e236c0e1f0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,17 +719,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -743,37 +744,37 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1589670000</t>
+          <t>17/05/2020 09:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -785,7 +786,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69ab2283-f832-4dfb-ad02-5aabeaacb0f5</t>
+          <t>94b00abc-bade-483e-8248-30c86bc8ce4a</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -820,17 +821,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1055.000000000000</t>
+          <t>1055.00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>945.000000000000</t>
+          <t>945.00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -845,37 +846,37 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1589670000</t>
+          <t>17/05/2020 09:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5.000000000000</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -887,7 +888,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6208984f-87cd-42e3-90f8-40199be7f8f3</t>
+          <t>609207dc-3f1d-4628-ba7b-9d3e0a0a9760</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -922,17 +923,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -948,32 +949,32 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -985,7 +986,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dfced0e6-ad49-40da-9b49-19923d2b4aef</t>
+          <t>d5af3795-d859-4917-8a36-5da76f17ddfd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1020,17 +1021,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1046,32 +1047,32 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1084,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6991c27d-e926-4eed-84f7-388dfda7e1c3</t>
+          <t>9ea4705a-5a90-409e-81b5-134a7c450f2b</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1118,17 +1119,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1050.000000000000</t>
+          <t>1050.00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>950.000000000000</t>
+          <t>950.00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1144,32 +1145,32 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>10.000000000000</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1182,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>e953c8f1-3d90-4e91-9e24-084b7bfd6ab4</t>
+          <t>8a5d9041-06ae-4c9c-9809-88e1413fe6f6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1216,17 +1217,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1242,32 +1243,32 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1280,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>b9626e5a-174a-4896-aed2-43c3d2790cc1</t>
+          <t>4880070f-87a3-4277-a418-aa3076d298c9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1314,17 +1315,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1340,32 +1341,32 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1378,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7aca9cc8-8212-4724-8ffb-bdf2b5dd8d02</t>
+          <t>951aaad0-d38a-4a31-93ae-279405a83821</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,17 +1413,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1438,32 +1439,32 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1476,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5c58b6c7-97bd-476f-945e-bdcbf6499caf</t>
+          <t>97a37bde-c0b2-473f-bdd4-9c48de7796fe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1510,17 +1511,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1040.000000000000</t>
+          <t>1040.00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>960.000000000000</t>
+          <t>960.00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1536,32 +1537,32 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>100.000000000000</t>
+          <t>100.00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2000.000000000000</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>940.000000000000</t>
+          <t>940.00</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -1582,4 +1583,1119 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Stored precision in AUD/quantities; no financial lifetime clipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>animal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>breed</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sex</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>age_weeks</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>estimated_age</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>mob</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>financial_complete</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>restriction_end</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>purchase</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>sale</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>feed</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>procedure</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TESTA00000000003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>6f1e4aba-15dd-4f6e-9dd2-3fcf3046f1da</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000003 (current); rfid:000000000000003 (current)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1589670000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TESTA00000000004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>c1cc6e28-6386-470a-944c-07e236c0e1f0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000004 (current); rfid:000000000000004 (current)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1589670000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TESTA00000000005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>94b00abc-bade-483e-8248-30c86bc8ce4a</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1055.000000000000</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>945.000000000000</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000005 (current); rfid:000000000000005 (current)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1589670000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>5.000000000000</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TESTA00000000006</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>609207dc-3f1d-4628-ba7b-9d3e0a0a9760</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000006 (current); rfid:000000000000006 (current)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TESTA00000000007</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>d5af3795-d859-4917-8a36-5da76f17ddfd</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000007 (current); rfid:000000000000007 (current)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TESTA00000000008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9ea4705a-5a90-409e-81b5-134a7c450f2b</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>STEER</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1050.000000000000</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>950.000000000000</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000008 (current); rfid:000000000000008 (current)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10.000000000000</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TESTA00000000009</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8a5d9041-06ae-4c9c-9809-88e1413fe6f6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000009 (current); rfid:000000000000009 (current)</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TESTA00000000010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4880070f-87a3-4277-a418-aa3076d298c9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000010 (current); rfid:000000000000010 (current)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TESTA00000000011</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>951aaad0-d38a-4a31-93ae-279405a83821</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000011 (current); rfid:000000000000011 (current)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TESTA00000000012</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>97a37bde-c0b2-473f-bdd4-9c48de7796fe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>exited</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Angus</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Unassigned / exited</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1040.000000000000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>960.000000000000</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>nlis:TESTA00000000012 (current); rfid:000000000000012 (current)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>100.000000000000</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2000.000000000000</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>940.000000000000</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>